--- a/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
+++ b/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,66 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5265,8 +5404,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U28"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -5289,1287 +5432,1398 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">궁초댕기 / 신고산 타령 — 민요채보-3/궁초댕기 신고산 타령.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">궁초댕기 / 신고산 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">감</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">잘</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">궁</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="P3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="E4" s="22"/>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G4" s="22"/>
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="N4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="P4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="T4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="U4" s="22"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="23"/>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="E5" s="23"/>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G5" s="23"/>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I5" s="23"/>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K5" s="23"/>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M5" s="23"/>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="P5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="U5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 仲</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="C6" s="20"/>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="20"/>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G6" s="20"/>
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 仲</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">댕</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K6" s="20"/>
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O6" s="20"/>
+      <c r="P6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="S6" s="20"/>
+      <c r="T6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="22"/>
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="22"/>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="22"/>
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="22"/>
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="K7" s="22"/>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="N7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="P7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">참</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="T7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="U7" s="22"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ‹</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="E8" s="23"/>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ‹</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="G8" s="23"/>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I8" s="23"/>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ‹</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K8" s="23"/>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M8" s="23"/>
+      <c r="N8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O8" s="23"/>
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="Q8" s="23"/>
+      <c r="R8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="S8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="U8" s="23"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="20"/>
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="20"/>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="20"/>
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="20"/>
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="O9" s="20"/>
+      <c r="P9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="R9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="S9" s="20"/>
+      <c r="T9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 汰</t>
         </is>
       </c>
-      <c r="U9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="U9" s="20"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E10" s="22"/>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K10" s="22"/>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="O10" s="22"/>
+      <c r="P10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S10" s="22"/>
+      <c r="T10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="U10" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="23"/>
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="E11" s="23"/>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G11" s="23"/>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I11" s="23"/>
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="K11" s="23"/>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M11" s="23"/>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">배</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q11" s="23"/>
+      <c r="R11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="S11" s="23"/>
+      <c r="T11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="U11" s="23"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="20"/>
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="I12" s="20"/>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K12" s="20"/>
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="O12" s="20"/>
+      <c r="P12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="U12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="T12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="U12" s="20"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="22"/>
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="E13" s="22"/>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I13" s="22"/>
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="K13" s="22"/>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">점</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="P13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="R13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">떠</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="T13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="U13" s="22"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="23"/>
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="23"/>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="23"/>
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="23"/>
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="23"/>
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="M14" s="23"/>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="P14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">봇</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="R14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="S14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="T14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">궁초댕기 / 신고산 타령 — 민요채보-3/궁초댕기 신고산 타령.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="U14" s="23"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">궁초댕기 / 신고산 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+      <c s="8" r="R16"/>
+      <c s="8" r="S16"/>
+      <c s="8" r="T16"/>
+      <c s="8" r="U16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="19"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="U17" s="20"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="19"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="U18" s="22"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="19"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="U19" s="23"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="19"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="24"/>
+      <c r="T20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="U20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="19"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="U21" s="22"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="19"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="U22" s="23"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="19"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="24"/>
+      <c r="T23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="U23" s="20"/>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="19"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="U24" s="22"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="19"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="U25" s="23"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="19"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="24"/>
+      <c r="T26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="U26" s="20"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="19"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="U27" s="22"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="19"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 ‹</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
+      <c r="U28" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
+++ b/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
@@ -417,7 +417,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -668,12 +668,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -869,14 +869,14 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|汰|―</t>
+          <t xml:space="preserve">㴌|汰|–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -910,14 +910,14 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌汰|無|―‹</t>
+          <t xml:space="preserve">㴌汰|無|–‹</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
-―‹</t>
+–‹</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -992,14 +992,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南|仲|―</t>
+          <t xml:space="preserve">無南|仲|–</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1113,13 +1113,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|汰</t>
+          <t xml:space="preserve">無|–|汰</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 汰</t>
         </is>
       </c>
@@ -1235,14 +1235,14 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌汰|無|―‹</t>
+          <t xml:space="preserve">㴌汰|無|–‹</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
-―‹</t>
+–‹</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1276,14 +1276,14 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|―</t>
+          <t xml:space="preserve">無|無|–</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1317,14 +1317,14 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|―</t>
+          <t xml:space="preserve">無|無|–</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1358,13 +1358,13 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|㴌</t>
+          <t xml:space="preserve">無|–|㴌</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 㴌</t>
         </is>
       </c>
@@ -1680,14 +1680,14 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|汰|―</t>
+          <t xml:space="preserve">㴌|汰|–</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I32" s="2"/>
@@ -1832,13 +1832,13 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―|㳞</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I35" s="2"/>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -1982,13 +1982,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―|㳞</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -2058,13 +2058,13 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―|㴌</t>
+          <t xml:space="preserve">㳞|–|㴌</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㴌</t>
         </is>
       </c>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㳞|㴌</t>
+          <t xml:space="preserve">–|㳞|㴌</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞
 㴌</t>
         </is>
@@ -2144,13 +2144,13 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―|無</t>
+          <t xml:space="preserve">汰|–|無</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 無</t>
         </is>
       </c>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌|汰</t>
+          <t xml:space="preserve">–|㴌|汰</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌
 汰</t>
         </is>
@@ -2230,13 +2230,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|南</t>
+          <t xml:space="preserve">無|–|南</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 南</t>
         </is>
       </c>
@@ -2311,14 +2311,14 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|―</t>
+          <t xml:space="preserve">無|無|–</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2352,14 +2352,14 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南|仲|―</t>
+          <t xml:space="preserve">無南|仲|–</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2473,13 +2473,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|汰</t>
+          <t xml:space="preserve">無|–|汰</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 汰</t>
         </is>
       </c>
@@ -2514,14 +2514,14 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|㳞|―</t>
+          <t xml:space="preserve">㳞|㳞|–</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2555,14 +2555,14 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|汰|―</t>
+          <t xml:space="preserve">㴌|汰|–</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌汰|無|―‹</t>
+          <t xml:space="preserve">㴌汰|無|–‹</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
-―‹</t>
+–‹</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2637,14 +2637,14 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|―</t>
+          <t xml:space="preserve">無|無|–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2678,13 +2678,13 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|南</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -2723,14 +2723,14 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|―</t>
+          <t xml:space="preserve">無|無|–</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2764,14 +2764,14 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|―</t>
+          <t xml:space="preserve">無|無|–</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I63" s="2"/>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I66" s="2"/>
@@ -3138,12 +3138,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I67" s="2"/>
@@ -3208,13 +3208,13 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|無</t>
+          <t xml:space="preserve">仲|–|無</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 無</t>
         </is>
       </c>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I70" s="2"/>
@@ -3284,14 +3284,14 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南|仲|―</t>
+          <t xml:space="preserve">無南|仲|–</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I72" s="2"/>
@@ -3360,12 +3360,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I73" s="2"/>
@@ -3430,14 +3430,14 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|―</t>
+          <t xml:space="preserve">無|無|–</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3672,14 +3672,14 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|汰|―</t>
+          <t xml:space="preserve">㴌|汰|–</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3713,14 +3713,14 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌汰|無|―</t>
+          <t xml:space="preserve">㴌汰|無|–</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I83" s="2"/>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I84" s="2"/>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I85" s="2"/>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3939,13 +3939,13 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―|無</t>
+          <t xml:space="preserve">汰|–|無</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 無</t>
         </is>
       </c>
@@ -4059,13 +4059,13 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―|㴌</t>
+          <t xml:space="preserve">汰|–|㴌</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 㴌</t>
         </is>
       </c>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|㳞|―</t>
+          <t xml:space="preserve">㳞|㳞|–</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4141,13 +4141,13 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―|汰</t>
+          <t xml:space="preserve">㴌|–|汰</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―
+–
 汰</t>
         </is>
       </c>
@@ -4186,13 +4186,13 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|南</t>
+          <t xml:space="preserve">無|–|南</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 南</t>
         </is>
       </c>
@@ -4231,13 +4231,13 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|南</t>
+          <t xml:space="preserve">無|–|南</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 南</t>
         </is>
       </c>
@@ -4268,13 +4268,13 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|姑</t>
+          <t xml:space="preserve">仲|–|姑</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -4461,7 +4461,7 @@
       <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 汰</t>
         </is>
       </c>
@@ -4473,7 +4473,7 @@
       <c r="N3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4513,7 +4513,7 @@
       <c r="B4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 無</t>
         </is>
       </c>
@@ -4546,7 +4546,7 @@
         <is>
           <t xml:space="preserve">㳞
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="9"/>
@@ -4566,7 +4566,7 @@
         <is>
           <t xml:space="preserve">㴌汰
 無
-―‹</t>
+–‹</t>
         </is>
       </c>
       <c r="S4" s="9" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="9"/>
@@ -4618,7 +4618,7 @@
         <is>
           <t xml:space="preserve">㴌
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="9"/>
@@ -4638,7 +4638,7 @@
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="S5" s="9" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="T5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U5" s="9"/>
@@ -4687,7 +4687,7 @@
         <is>
           <t xml:space="preserve">㴌汰
 無
-―‹</t>
+–‹</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
@@ -4707,7 +4707,7 @@
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="T6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U6" s="10"/>
@@ -4727,7 +4727,7 @@
       <c r="B7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 㴌</t>
         </is>
       </c>
@@ -4744,7 +4744,7 @@
         <is>
           <t xml:space="preserve">㴌
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -4767,7 +4767,7 @@
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -4778,7 +4778,7 @@
       <c r="N7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㳞</t>
         </is>
       </c>
@@ -4792,7 +4792,7 @@
       <c r="R7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 㴌</t>
         </is>
       </c>
@@ -4820,7 +4820,7 @@
         <is>
           <t xml:space="preserve">㳞
 㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4836,7 +4836,7 @@
         <is>
           <t xml:space="preserve">㴌汰
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -4846,14 +4846,14 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 南</t>
         </is>
       </c>
@@ -4896,7 +4896,7 @@
       <c r="B9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―
+–
 汰</t>
         </is>
       </c>
@@ -4911,13 +4911,13 @@
       <c r="G9" s="9"/>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K9" s="9"/>
@@ -4925,7 +4925,7 @@
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -4936,7 +4936,7 @@
       <c r="N9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―
+–
 㴌</t>
         </is>
       </c>
@@ -4975,7 +4975,7 @@
       <c r="B10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 南</t>
         </is>
       </c>
@@ -4990,7 +4990,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="10"/>
@@ -5004,7 +5004,7 @@
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞
 㴌</t>
         </is>
@@ -5054,7 +5054,7 @@
       <c r="B11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 南</t>
         </is>
       </c>
@@ -5065,14 +5065,14 @@
       <c r="G11" s="8"/>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 無</t>
         </is>
       </c>
@@ -5094,7 +5094,7 @@
       <c r="N11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 無</t>
         </is>
       </c>
@@ -5119,7 +5119,7 @@
         <is>
           <t xml:space="preserve">㴌
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="U11" s="8" t="inlineStr">
@@ -5133,7 +5133,7 @@
       <c r="B12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 姑</t>
         </is>
       </c>
@@ -5144,14 +5144,14 @@
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K12" s="9"/>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="N12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌
 汰</t>
         </is>
@@ -5193,7 +5193,7 @@
         <is>
           <t xml:space="preserve">㴌汰
 無
-―‹</t>
+–‹</t>
         </is>
       </c>
       <c r="U12" s="9" t="inlineStr">
@@ -5220,7 +5220,7 @@
         <is>
           <t xml:space="preserve">無南
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -5233,7 +5233,7 @@
       <c r="N13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 南</t>
         </is>
       </c>
@@ -5286,7 +5286,7 @@
       <c r="I14" s="10"/>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="10"/>
@@ -5321,7 +5321,7 @@
         <is>
           <t xml:space="preserve">無南
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="U14" s="10" t="inlineStr">
@@ -5342,7 +5342,7 @@
       <c r="I15" s="8"/>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K15" s="8"/>
@@ -5352,7 +5352,7 @@
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr">
@@ -5366,7 +5366,7 @@
         <is>
           <t xml:space="preserve">㴌
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="S15" s="8" t="inlineStr">
@@ -5409,7 +5409,7 @@
         <is>
           <t xml:space="preserve">無南
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="O16" s="9" t="inlineStr">
@@ -5455,7 +5455,7 @@
         <is>
           <t xml:space="preserve">無
 無
-―</t>
+–</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -5481,14 +5481,14 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S17" s="9"/>
       <c r="T17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 汰</t>
         </is>
       </c>

--- a/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
+++ b/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4393,116 +4434,116 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">궁초댕기 신고산 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가스</t>
         </is>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="D3" s="23"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 無</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">열두고</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 㴌汰</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">청진</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –
 汰</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">웃</t>
         </is>
       </c>
-      <c r="N3" s="18" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –
 㳞</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">궁초</t>
         </is>
       </c>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="P3" s="23"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="S3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">싼다</t>
         </is>
       </c>
-      <c r="T3" s="17" t="inlineStr">
+      <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
 㳞</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="U3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">신고산</t>
         </is>
@@ -4510,305 +4551,305 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –
 無</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">러기</t>
         </is>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="D4" s="23"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="26"/>
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
 –</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">으며</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="O4" s="26"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
 –‹</t>
         </is>
       </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="S4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="T4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="U4" s="9"/>
+      <c r="U4" s="26"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="D5" s="23"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">단</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="26"/>
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰
 –</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">오리</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="9"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="O5" s="26"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 –</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="S5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어랑</t>
         </is>
       </c>
-      <c r="T5" s="17" t="inlineStr">
+      <c r="T5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U5" s="9"/>
+      <c r="U5" s="26"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 △</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="C6" s="27"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">숨에</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="27"/>
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
 –‹</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="O6" s="27"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 –</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">어랑</t>
         </is>
       </c>
-      <c r="T6" s="17" t="inlineStr">
+      <c r="T6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U6" s="10"/>
+      <c r="U6" s="27"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –
 㴌</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">남대</t>
         </is>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="D7" s="23"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰
 –</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">올라</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 –</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="M7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">무슨</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –
 㳞</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">댕기</t>
         </is>
       </c>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="18" t="inlineStr">
+      <c r="P7" s="23"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –
 㴌</t>
         </is>
       </c>
-      <c r="S7" s="11" t="inlineStr">
+      <c r="S7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어허</t>
         </is>
       </c>
-      <c r="T7" s="18" t="inlineStr">
+      <c r="T7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞
 㳞</t>
         </is>
       </c>
-      <c r="U7" s="11" t="inlineStr">
+      <c r="U7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우르르</t>
         </is>
@@ -4816,76 +4857,76 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
 –</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">천에</t>
         </is>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="D8" s="23"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
 –</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="K8" s="26"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –
 南</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
+      <c r="M8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">짝에</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">‹</t>
         </is>
       </c>
-      <c r="O8" s="9"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="O8" s="26"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S8" s="9" t="inlineStr">
+      <c r="S8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="T8" s="17" t="inlineStr">
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="U8" s="9" t="inlineStr">
+      <c r="U8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
@@ -4893,78 +4934,78 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –
 汰</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">서스</t>
         </is>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="D9" s="23"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="26"/>
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="K9" s="26"/>
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 –</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">무슨</t>
         </is>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –
 㴌</t>
         </is>
       </c>
-      <c r="O9" s="12" t="inlineStr">
+      <c r="O9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">단장</t>
         </is>
       </c>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="P9" s="23"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S9" s="9" t="inlineStr">
+      <c r="S9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="T9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌
 汰</t>
         </is>
       </c>
-      <c r="U9" s="9" t="inlineStr">
+      <c r="U9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">함흥</t>
         </is>
@@ -4972,78 +5013,78 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –
 南</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">러미</t>
         </is>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="D10" s="23"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="27"/>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△‹</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="27"/>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 –</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">짝에</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㳞
 㴌</t>
         </is>
       </c>
-      <c r="O10" s="10" t="inlineStr">
+      <c r="O10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">하고</t>
         </is>
       </c>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="P10" s="23"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="T10" s="17" t="inlineStr">
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
 㳞</t>
         </is>
       </c>
-      <c r="U10" s="10" t="inlineStr">
+      <c r="U10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">차떠나는</t>
         </is>
@@ -5051,78 +5092,78 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –
 南</t>
         </is>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="C11" s="24"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="24"/>
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 無</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –
 無</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">신고</t>
         </is>
       </c>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="P11" s="23"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
+      <c r="S11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="T11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰
 –</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
+      <c r="U11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">소리</t>
         </is>
@@ -5130,73 +5171,73 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 姑</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="C12" s="26"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="26"/>
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="K12" s="26"/>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">령</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌
 汰</t>
         </is>
       </c>
-      <c r="O12" s="9" t="inlineStr">
+      <c r="O12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">산비</t>
         </is>
       </c>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="P12" s="23"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S12" s="9" t="inlineStr">
+      <c r="S12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="T12" s="17" t="inlineStr">
+      <c r="T12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
 –‹</t>
         </is>
       </c>
-      <c r="U12" s="9" t="inlineStr">
+      <c r="U12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5204,66 +5245,66 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲
 –</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="L13" s="23"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –
 南</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">올때</t>
         </is>
       </c>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="P13" s="23"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰
 無</t>
         </is>
       </c>
-      <c r="S13" s="9" t="inlineStr">
+      <c r="S13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 無</t>
         </is>
       </c>
-      <c r="U13" s="9" t="inlineStr">
+      <c r="U13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">잠못드</t>
         </is>
@@ -5271,60 +5312,60 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 △</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲南
 △‹</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에는</t>
         </is>
       </c>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="P14" s="23"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㴌
 㳞</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="T14" s="17" t="inlineStr">
+      <c r="T14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲
 –</t>
         </is>
       </c>
-      <c r="U14" s="10" t="inlineStr">
+      <c r="U14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -5332,56 +5373,56 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="K15" s="24"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 –</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">한아</t>
         </is>
       </c>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="17" t="inlineStr">
+      <c r="P15" s="23"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰
 –</t>
         </is>
       </c>
-      <c r="S15" s="8" t="inlineStr">
+      <c r="S15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="T15" s="17" t="inlineStr">
+      <c r="T15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 無</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="U15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">큰애기</t>
         </is>
@@ -5389,53 +5430,53 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="B16" s="23"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">‹</t>
         </is>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="K16" s="26"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲
 –</t>
         </is>
       </c>
-      <c r="O16" s="9" t="inlineStr">
+      <c r="O16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">름</t>
         </is>
       </c>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="17" t="inlineStr">
+      <c r="P16" s="23"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無</t>
         </is>
       </c>
-      <c r="S16" s="9" t="inlineStr">
+      <c r="S16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="T16" s="17" t="inlineStr">
+      <c r="T16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無‹</t>
         </is>
       </c>
-      <c r="U16" s="9" t="inlineStr">
+      <c r="U16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -5443,56 +5484,56 @@
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="B17" s="23"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 –</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">신고</t>
         </is>
       </c>
-      <c r="L17" s="17"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="L17" s="23"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 無</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="O17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃을안</t>
         </is>
       </c>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="17" t="inlineStr">
+      <c r="P17" s="23"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S17" s="9"/>
-      <c r="T17" s="17" t="inlineStr">
+      <c r="S17" s="26"/>
+      <c r="T17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –
 汰</t>
         </is>
       </c>
-      <c r="U17" s="9" t="inlineStr">
+      <c r="U17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">반봇</t>
         </is>
@@ -5500,59 +5541,59 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="B18" s="23"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr">
+      <c r="K18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="M18" s="27"/>
+      <c r="N18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O18" s="10" t="inlineStr">
+      <c r="O18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="17" t="inlineStr">
+      <c r="P18" s="23"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 △</t>
         </is>
       </c>
-      <c r="S18" s="10"/>
-      <c r="T18" s="17" t="inlineStr">
+      <c r="S18" s="27"/>
+      <c r="T18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㴌
 仲</t>
         </is>
       </c>
-      <c r="U18" s="10" t="inlineStr">
+      <c r="U18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">짐만</t>
         </is>

--- a/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
+++ b/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
@@ -4407,32 +4407,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="U4" s="26"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="U5" s="26"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O6" s="27"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="U6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23"/>
       <c r="C16" s="26"/>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
       <c r="C17" s="26"/>
@@ -5539,7 +5539,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
       <c r="C18" s="27"/>

--- a/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
+++ b/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
@@ -951,14 +951,14 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌汰|無|–‹</t>
+          <t xml:space="preserve">㴌汰|無|–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1276,14 +1276,14 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌汰|無|–‹</t>
+          <t xml:space="preserve">㴌汰|無|–</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1837,13 +1837,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚|△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I33" s="2"/>
@@ -2064,12 +2063,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I39" s="2"/>
@@ -2312,13 +2311,13 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲南|△‹</t>
+          <t xml:space="preserve">仲南|△</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲南
-△‹</t>
+△</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2637,14 +2636,14 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌汰|無|–‹</t>
+          <t xml:space="preserve">㴌汰|無|–</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
 無
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3214,12 +3213,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△‹</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△‹</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I68" s="2"/>
@@ -3436,12 +3435,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I74" s="2"/>
@@ -4064,13 +4063,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚|△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I90" s="2"/>
@@ -4385,13 +4383,12 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚|△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I98" s="2"/>
@@ -4607,7 +4604,7 @@
         <is>
           <t xml:space="preserve">㴌汰
 無
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="S4" s="26" t="inlineStr">
@@ -4698,8 +4695,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="C6" s="27"/>
@@ -4728,7 +4724,7 @@
         <is>
           <t xml:space="preserve">㴌汰
 無
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="M6" s="27" t="inlineStr">
@@ -4905,7 +4901,7 @@
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="O8" s="26"/>
@@ -5037,7 +5033,7 @@
       <c r="I10" s="27"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">△‹</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="K10" s="27"/>
@@ -5234,7 +5230,7 @@
         <is>
           <t xml:space="preserve">㴌汰
 無
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="U12" s="26" t="inlineStr">
@@ -5314,8 +5310,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="C14" s="27"/>
@@ -5336,7 +5331,7 @@
       <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲南
-△‹</t>
+△</t>
         </is>
       </c>
       <c r="O14" s="27" t="inlineStr">
@@ -5440,7 +5435,7 @@
       <c r="I16" s="26"/>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K16" s="26"/>
@@ -5473,7 +5468,7 @@
       </c>
       <c r="T16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="U16" s="26" t="inlineStr">
@@ -5581,8 +5576,7 @@
       <c r="Q18" s="27"/>
       <c r="R18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="S18" s="27"/>

--- a/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
+++ b/sheets/민요/검수/궁초댕기 신고산 타령.xlsx
@@ -4466,7 +4466,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">가스</t>
+          <t xml:space="preserve">가
+스</t>
         </is>
       </c>
       <c r="D3" s="23"/>
@@ -4482,7 +4483,9 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">열두고</t>
+          <t xml:space="preserve">열
+두
+고</t>
         </is>
       </c>
       <c r="J3" s="23" t="inlineStr">
@@ -4493,7 +4496,8 @@
       </c>
       <c r="K3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">청진</t>
+          <t xml:space="preserve">청
+진</t>
         </is>
       </c>
       <c r="L3" s="23" t="inlineStr">
@@ -4517,7 +4521,8 @@
       </c>
       <c r="O3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">궁초</t>
+          <t xml:space="preserve">궁
+초</t>
         </is>
       </c>
       <c r="P3" s="23"/>
@@ -4530,7 +4535,8 @@
       </c>
       <c r="S3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">싼다</t>
+          <t xml:space="preserve">싼
+다</t>
         </is>
       </c>
       <c r="T3" s="23" t="inlineStr">
@@ -4542,7 +4548,9 @@
       </c>
       <c r="U3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">신고산</t>
+          <t xml:space="preserve">신
+고
+산</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4565,8 @@
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">러기</t>
+          <t xml:space="preserve">러
+기</t>
         </is>
       </c>
       <c r="D4" s="23"/>
@@ -4589,7 +4598,8 @@
       </c>
       <c r="M4" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">으며</t>
+          <t xml:space="preserve">으
+며</t>
         </is>
       </c>
       <c r="N4" s="23" t="inlineStr">
@@ -4661,7 +4671,8 @@
       </c>
       <c r="M5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">오리</t>
+          <t xml:space="preserve">오
+리</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
@@ -4681,7 +4692,8 @@
       </c>
       <c r="S5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">어랑</t>
+          <t xml:space="preserve">어
+랑</t>
         </is>
       </c>
       <c r="T5" s="23" t="inlineStr">
@@ -4711,7 +4723,8 @@
       </c>
       <c r="I6" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">숨에</t>
+          <t xml:space="preserve">숨
+에</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
@@ -4749,7 +4762,8 @@
       </c>
       <c r="S6" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">어랑</t>
+          <t xml:space="preserve">어
+랑</t>
         </is>
       </c>
       <c r="T6" s="23" t="inlineStr">
@@ -4770,7 +4784,8 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">남대</t>
+          <t xml:space="preserve">남
+대</t>
         </is>
       </c>
       <c r="D7" s="23"/>
@@ -4786,7 +4801,8 @@
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">올라</t>
+          <t xml:space="preserve">올
+라</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -4809,7 +4825,8 @@
       </c>
       <c r="M7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">무슨</t>
+          <t xml:space="preserve">무
+슨</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
@@ -4821,7 +4838,8 @@
       </c>
       <c r="O7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">댕기</t>
+          <t xml:space="preserve">댕
+기</t>
         </is>
       </c>
       <c r="P7" s="23"/>
@@ -4835,7 +4853,8 @@
       </c>
       <c r="S7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">어허</t>
+          <t xml:space="preserve">어
+허</t>
         </is>
       </c>
       <c r="T7" s="21" t="inlineStr">
@@ -4847,7 +4866,9 @@
       </c>
       <c r="U7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우르르</t>
+          <t xml:space="preserve">우
+르
+르</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4883,8 @@
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">천에</t>
+          <t xml:space="preserve">천
+에</t>
         </is>
       </c>
       <c r="D8" s="23"/>
@@ -4896,7 +4918,8 @@
       </c>
       <c r="M8" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">짝에</t>
+          <t xml:space="preserve">짝
+에</t>
         </is>
       </c>
       <c r="N8" s="23" t="inlineStr">
@@ -4939,7 +4962,8 @@
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">서스</t>
+          <t xml:space="preserve">서
+스</t>
         </is>
       </c>
       <c r="D9" s="23"/>
@@ -4967,7 +4991,8 @@
       </c>
       <c r="M9" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">무슨</t>
+          <t xml:space="preserve">무
+슨</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -4979,7 +5004,8 @@
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">단장</t>
+          <t xml:space="preserve">단
+장</t>
         </is>
       </c>
       <c r="P9" s="23"/>
@@ -5003,7 +5029,8 @@
       </c>
       <c r="U9" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">함흥</t>
+          <t xml:space="preserve">함
+흥</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5045,8 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">러미</t>
+          <t xml:space="preserve">러
+미</t>
         </is>
       </c>
       <c r="D10" s="23"/>
@@ -5046,7 +5074,8 @@
       </c>
       <c r="M10" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">짝에</t>
+          <t xml:space="preserve">짝
+에</t>
         </is>
       </c>
       <c r="N10" s="23" t="inlineStr">
@@ -5058,7 +5087,8 @@
       </c>
       <c r="O10" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">하고</t>
+          <t xml:space="preserve">하
+고</t>
         </is>
       </c>
       <c r="P10" s="23"/>
@@ -5082,7 +5112,10 @@
       </c>
       <c r="U10" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">차떠나는</t>
+          <t xml:space="preserve">차
+떠
+나
+는</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5170,8 @@
       </c>
       <c r="O11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">신고</t>
+          <t xml:space="preserve">신
+고</t>
         </is>
       </c>
       <c r="P11" s="23"/>
@@ -5161,7 +5195,8 @@
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">소
+리</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5246,8 @@
       </c>
       <c r="O12" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">산비</t>
+          <t xml:space="preserve">산
+비</t>
         </is>
       </c>
       <c r="P12" s="23"/>
@@ -5276,7 +5312,8 @@
       </c>
       <c r="O13" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">올때</t>
+          <t xml:space="preserve">올
+때</t>
         </is>
       </c>
       <c r="P13" s="23"/>
@@ -5302,7 +5339,9 @@
       </c>
       <c r="U13" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">잠못드</t>
+          <t xml:space="preserve">잠
+못
+드</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5375,8 @@
       </c>
       <c r="O14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">에는</t>
+          <t xml:space="preserve">에
+는</t>
         </is>
       </c>
       <c r="P14" s="23"/>
@@ -5393,7 +5433,8 @@
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">한아</t>
+          <t xml:space="preserve">한
+아</t>
         </is>
       </c>
       <c r="P15" s="23"/>
@@ -5419,7 +5460,9 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">큰애기</t>
+          <t xml:space="preserve">큰
+애
+기</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5539,8 @@
       </c>
       <c r="K17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">신고</t>
+          <t xml:space="preserve">신
+고</t>
         </is>
       </c>
       <c r="L17" s="23"/>
@@ -5510,7 +5554,9 @@
       </c>
       <c r="O17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃을안</t>
+          <t xml:space="preserve">꽃
+을
+안</t>
         </is>
       </c>
       <c r="P17" s="23"/>
@@ -5530,7 +5576,8 @@
       </c>
       <c r="U17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">반봇</t>
+          <t xml:space="preserve">반
+봇</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5636,8 @@
       </c>
       <c r="U18" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">짐만</t>
+          <t xml:space="preserve">짐
+만</t>
         </is>
       </c>
     </row>
